--- a/output/2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,6 @@
           <t>GROTA d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Krk</t>
@@ -574,7 +573,6 @@
           <t>051 221 511</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Commercio di utensili, macchine utensili e ferramenta (anche vernici e prodotti agricoli/sementi); nessun sito proprio individuato</t>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -624,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -666,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -696,7 +694,6 @@
           <t>+385 51 628 588</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Commercio di cuscinetti, cinghie, guarnizioni, adesivi industriali per assemblaggio/manutenzione macchine; distributore ufficiale SKF dal 1990</t>
@@ -704,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -746,7 +743,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -788,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -818,7 +815,6 @@
           <t>051 207 900</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Ingrosso/dettaglio materiali di riproduzione per metallurgia ferrosa e non ferrosa (tubi, barre, profili, lamiere, elementi forgiati, viteria, tecnologia di saldatura)</t>
@@ -826,7 +822,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -868,7 +864,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
